--- a/offers/seasonal/عروض اليوم الوطني باير.xlsx
+++ b/offers/seasonal/عروض اليوم الوطني باير.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7121193E-67ED-46DA-B1AE-53BEAA05BC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D01DEEC-DE64-4454-B060-D948BB9B8BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -43,103 +43,52 @@
     <t>نوع العرض</t>
   </si>
   <si>
-    <t>00044183</t>
-  </si>
-  <si>
     <t>PRIORIN Steel 60's</t>
   </si>
   <si>
-    <t>00046694</t>
-  </si>
-  <si>
     <t>Bepanthen Cracked Skin OINT 100g</t>
   </si>
   <si>
-    <t>00016742</t>
-  </si>
-  <si>
     <t>BEPANTHEN CREAM 5% 100G EFA</t>
   </si>
   <si>
-    <t>00017043</t>
-  </si>
-  <si>
     <t>BEPANTHEN OINT 5% TUBE 100G EFA</t>
   </si>
   <si>
-    <t>00017464</t>
-  </si>
-  <si>
     <t>78_Priorin CAPS 90</t>
   </si>
   <si>
-    <t>0003244</t>
-  </si>
-  <si>
     <t>REDOXON OR SS TAEF 15 GA-1400/460 EFA</t>
   </si>
   <si>
-    <t>00044182</t>
-  </si>
-  <si>
     <t>Redoxon Triple Actions 15's</t>
   </si>
   <si>
-    <t>00046692</t>
-  </si>
-  <si>
     <t>Redoxon Immuno Complete</t>
   </si>
   <si>
-    <t>00046695</t>
-  </si>
-  <si>
     <t>16_Bepanthen Cream 5% 50G</t>
   </si>
   <si>
-    <t>00022556</t>
-  </si>
-  <si>
     <t>BPN Gentle BodyCleanser GEL BT 400ml MEA</t>
   </si>
   <si>
-    <t>00022557</t>
-  </si>
-  <si>
     <t>BPN Gentle FaceCleanser GEL BT 200ml MEA</t>
   </si>
   <si>
-    <t>00022554</t>
-  </si>
-  <si>
     <t>BPN Regenerate NightFace CREA BT50ml MEA</t>
   </si>
   <si>
-    <t>0004450</t>
-  </si>
-  <si>
     <t>BPN Replenish body CREA TUF 200ml MEA</t>
   </si>
   <si>
-    <t>00023665</t>
-  </si>
-  <si>
     <t>BPN Replenish Body CREA BT 400ml MEA</t>
   </si>
   <si>
-    <t>00022553</t>
-  </si>
-  <si>
     <t>BPN Restore Body LOTI TUF 200ml MEA</t>
   </si>
   <si>
-    <t>00022555</t>
-  </si>
-  <si>
     <t>BPN Restore Body LOTI BT 400ml MEA</t>
-  </si>
-  <si>
-    <t>00022552</t>
   </si>
   <si>
     <t>BPN Restore Face SPF25 CREA BT 50ml MEA</t>
@@ -210,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -229,6 +178,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,11 +554,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8">
+        <v>44183</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="3">
         <v>194.35</v>
@@ -623,15 +573,15 @@
         <v>46285</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
+      <c r="A3" s="8">
+        <v>46694</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3">
         <v>79.930000000000007</v>
@@ -646,15 +596,15 @@
         <v>46285</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
+      <c r="A4" s="8">
+        <v>16742</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3">
         <v>74.98</v>
@@ -669,15 +619,15 @@
         <v>46285</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
+      <c r="A5" s="8">
+        <v>17043</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>54.86</v>
@@ -692,15 +642,15 @@
         <v>46285</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
+      <c r="A6" s="8">
+        <v>17464</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>86.55</v>
@@ -715,15 +665,15 @@
         <v>46285</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
+      <c r="A7" s="8">
+        <v>3244</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3">
         <v>28.75</v>
@@ -738,15 +688,15 @@
         <v>46285</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
+      <c r="A8" s="8">
+        <v>44182</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>34.5</v>
@@ -761,15 +711,15 @@
         <v>46285</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
+      <c r="A9" s="8">
+        <v>46692</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>39.68</v>
@@ -784,15 +734,15 @@
         <v>46285</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
+      <c r="A10" s="8">
+        <v>46695</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>41.98</v>
@@ -807,15 +757,15 @@
         <v>46285</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
+      <c r="A11" s="8">
+        <v>22556</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
         <v>119.6</v>
@@ -830,15 +780,15 @@
         <v>46285</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
+      <c r="A12" s="8">
+        <v>22557</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3">
         <v>74.75</v>
@@ -853,15 +803,15 @@
         <v>46285</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
+      <c r="A13" s="8">
+        <v>22554</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>109.25</v>
@@ -876,15 +826,15 @@
         <v>46285</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>31</v>
+      <c r="A14" s="8">
+        <v>4450</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <v>101.2</v>
@@ -899,15 +849,15 @@
         <v>46285</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>33</v>
+      <c r="A15" s="8">
+        <v>23665</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>182.16</v>
@@ -922,15 +872,15 @@
         <v>46285</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
+      <c r="A16" s="8">
+        <v>22553</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3">
         <v>94.3</v>
@@ -945,15 +895,15 @@
         <v>46285</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>37</v>
+      <c r="A17" s="8">
+        <v>22555</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
         <v>155.25</v>
@@ -968,15 +918,15 @@
         <v>46285</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>39</v>
+      <c r="A18" s="8">
+        <v>22552</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3">
         <v>112.7</v>
@@ -991,7 +941,7 @@
         <v>46285</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
